--- a/contest_entry_forms/016_halloween_horse_show_entry_form--contest_entry_forms.xlsx
+++ b/contest_entry_forms/016_halloween_horse_show_entry_form--contest_entry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -946,29 +946,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>quarter_horse</t>
+          <t>warmblood</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Quarter Horse</t>
+          <t>Warmblood</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>breed_choices</t>
+          <t>division_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>warmblood</t>
+          <t>hunter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Warmblood</t>
+          <t>Hunter</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hunter</t>
+          <t>jumper</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Jumper</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jumper</t>
+          <t>hunter/jumper</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jumper</t>
+          <t>Hunter/Jumper</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hunter/jumper</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hunter/Jumper</t>
+          <t>Hack</t>
         </is>
       </c>
     </row>
@@ -1031,29 +1031,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>hack/_hunter/jumper</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Hack/ Hunter/Jumper</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>division_choices</t>
+          <t>class_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hack/_hunter/jumper</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hack/ Hunter/Jumper</t>
+          <t>Junior</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>junior</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>senior</t>
+          <t>amateur</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Amateur</t>
         </is>
       </c>
     </row>
@@ -1099,29 +1099,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>amateur</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amateur</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>class_choices</t>
+          <t>show_type_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>dressage</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dressage</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dressage</t>
+          <t>hunter</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dressage</t>
+          <t>Hunter</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hunter</t>
+          <t>hunter_jumper</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Hunter Jumper</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hunter_jumper</t>
+          <t>hunter/jumper</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hunter Jumper</t>
+          <t>Hunter/Jumper</t>
         </is>
       </c>
     </row>
@@ -1184,27 +1184,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hunter/jumper</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>Hunter/Jumper</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>show_type_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
